--- a/static/data/exports/Retro_AS_AE_2026.xlsx
+++ b/static/data/exports/Retro_AS_AE_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_AE_2026.xlsx
+++ b/static/data/exports/Retro_AS_AE_2026.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -9370,7 +9370,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12185,7 +12185,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -16447,7 +16447,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O246" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -19655,7 +19655,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -20421,7 +20421,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -22195,7 +22195,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -25141,7 +25141,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -26326,7 +26326,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -26398,7 +26398,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -26542,7 +26542,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -27380,7 +27380,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -27799,7 +27799,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -27871,7 +27871,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -28002,7 +28002,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O394" t="inlineStr">
@@ -28146,7 +28146,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -28290,7 +28290,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -28781,7 +28781,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -29056,7 +29056,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -29128,7 +29128,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O410" t="inlineStr">
@@ -29272,7 +29272,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -29416,7 +29416,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -29560,7 +29560,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -29763,7 +29763,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O418" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -30385,7 +30385,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -30457,7 +30457,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -30529,7 +30529,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -30660,7 +30660,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -31092,7 +31092,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -31308,7 +31308,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -31583,7 +31583,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -31714,7 +31714,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -31786,7 +31786,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O447" t="inlineStr">
@@ -31858,7 +31858,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -32133,7 +32133,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -32205,7 +32205,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -32349,7 +32349,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -32421,7 +32421,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -32493,7 +32493,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -32912,7 +32912,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -33331,7 +33331,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -33606,7 +33606,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -33953,7 +33953,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -34228,7 +34228,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -34719,7 +34719,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -34994,7 +34994,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -35138,7 +35138,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -35269,7 +35269,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -35341,7 +35341,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O498" t="inlineStr">
@@ -35413,7 +35413,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O499" t="inlineStr">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O500" t="inlineStr">
@@ -35557,7 +35557,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O501" t="inlineStr">
@@ -35688,7 +35688,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O503" t="inlineStr">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O504" t="inlineStr">
@@ -35832,7 +35832,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O505" t="inlineStr">
@@ -35904,7 +35904,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O506" t="inlineStr">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O507" t="inlineStr">
@@ -36048,7 +36048,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O508" t="inlineStr">
@@ -36467,7 +36467,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O514" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O515" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -36742,7 +36742,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O518" t="inlineStr">
@@ -37652,7 +37652,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O531" t="inlineStr">
@@ -37724,7 +37724,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -37796,7 +37796,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -37868,7 +37868,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -38143,7 +38143,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O538" t="inlineStr">
@@ -38418,7 +38418,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O545" t="inlineStr">
@@ -38765,7 +38765,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -38837,7 +38837,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O548" t="inlineStr">
@@ -38909,7 +38909,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -39184,7 +39184,7 @@
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O553" t="inlineStr">
@@ -39315,7 +39315,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -39459,7 +39459,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -39590,7 +39590,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O559" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
@@ -39734,7 +39734,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O562" t="inlineStr">
@@ -39937,7 +39937,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -40009,7 +40009,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
@@ -40225,7 +40225,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O568" t="inlineStr">
@@ -40297,7 +40297,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -40428,7 +40428,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O571" t="inlineStr">
@@ -40500,7 +40500,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -40572,7 +40572,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O573" t="inlineStr">
@@ -40644,7 +40644,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O574" t="inlineStr">
@@ -40716,7 +40716,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O575" t="inlineStr">
@@ -40788,7 +40788,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O577" t="inlineStr">
@@ -40932,7 +40932,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O578" t="inlineStr">
@@ -41063,7 +41063,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -41135,7 +41135,7 @@
       </c>
       <c r="N581" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O581" t="inlineStr">
@@ -41207,7 +41207,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O582" t="inlineStr">
@@ -41279,7 +41279,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O583" t="inlineStr">
@@ -41410,7 +41410,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -41482,7 +41482,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -41554,7 +41554,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O587" t="inlineStr">
@@ -41685,7 +41685,7 @@
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O589" t="inlineStr">
@@ -41757,7 +41757,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O590" t="inlineStr">
@@ -41829,7 +41829,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O591" t="inlineStr">
@@ -41901,7 +41901,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O592" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O594" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
@@ -42176,7 +42176,7 @@
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O596" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O598" t="inlineStr">
@@ -42379,7 +42379,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O599" t="inlineStr">
@@ -42451,7 +42451,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
@@ -42654,7 +42654,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O603" t="inlineStr">
@@ -42726,7 +42726,7 @@
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O604" t="inlineStr">
@@ -42798,7 +42798,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -42870,7 +42870,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -43001,7 +43001,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -43073,7 +43073,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
@@ -43145,7 +43145,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -43276,7 +43276,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
@@ -43348,7 +43348,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -43420,7 +43420,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
@@ -43551,7 +43551,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -43695,7 +43695,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
@@ -43826,7 +43826,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
@@ -43898,7 +43898,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -43970,7 +43970,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
@@ -44186,7 +44186,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
@@ -44258,7 +44258,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
@@ -44330,7 +44330,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O627" t="inlineStr">
@@ -44461,7 +44461,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -44533,7 +44533,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
@@ -44605,7 +44605,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -44677,7 +44677,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
@@ -45096,7 +45096,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -45299,7 +45299,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -45371,7 +45371,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -45502,7 +45502,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
@@ -45646,7 +45646,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O646" t="inlineStr">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -45849,7 +45849,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
@@ -45921,7 +45921,7 @@
       </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="N651" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O651" t="inlineStr">
@@ -46065,7 +46065,7 @@
       </c>
       <c r="N652" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
@@ -46137,7 +46137,7 @@
       </c>
       <c r="N653" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O653" t="inlineStr">
@@ -46268,7 +46268,7 @@
       </c>
       <c r="N655" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
@@ -46340,7 +46340,7 @@
       </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
@@ -46412,7 +46412,7 @@
       </c>
       <c r="N657" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O657" t="inlineStr">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
@@ -46615,7 +46615,7 @@
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O660" t="inlineStr">
@@ -46687,7 +46687,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
@@ -46759,7 +46759,7 @@
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O662" t="inlineStr">
@@ -46890,7 +46890,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O664" t="inlineStr">
@@ -46962,7 +46962,7 @@
       </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
@@ -47106,7 +47106,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
@@ -47178,7 +47178,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O668" t="inlineStr">
@@ -47309,7 +47309,7 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O670" t="inlineStr">
@@ -47381,7 +47381,7 @@
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O671" t="inlineStr">
@@ -47453,7 +47453,7 @@
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O672" t="inlineStr">
@@ -47525,7 +47525,7 @@
       </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O673" t="inlineStr">
@@ -47656,7 +47656,7 @@
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O675" t="inlineStr">
@@ -47728,7 +47728,7 @@
       </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O676" t="inlineStr">
@@ -47800,7 +47800,7 @@
       </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O677" t="inlineStr">
@@ -47872,7 +47872,7 @@
       </c>
       <c r="N678" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O678" t="inlineStr">
@@ -47944,7 +47944,7 @@
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
@@ -50373,7 +50373,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -50445,7 +50445,7 @@
       </c>
       <c r="N715" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
@@ -50576,7 +50576,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -50648,7 +50648,7 @@
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O718" t="inlineStr">
@@ -50720,7 +50720,7 @@
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
@@ -50851,7 +50851,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
@@ -50923,7 +50923,7 @@
       </c>
       <c r="N722" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
@@ -50995,7 +50995,7 @@
       </c>
       <c r="N723" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O723" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
@@ -51198,7 +51198,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
@@ -51270,7 +51270,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
@@ -51342,7 +51342,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -51439,11 +51439,11 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>1961718</v>
+        <v>1961717</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Nasir Uddin Barbhuiya</t>
+          <t>Nurul Alom Barbhuiya</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -51476,7 +51476,7 @@
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>Nasir Uddin Barbhuiya</t>
+          <t>Nurul Alom Barbhuiya</t>
         </is>
       </c>
       <c r="L730" t="inlineStr">
@@ -51486,7 +51486,7 @@
       </c>
       <c r="N730" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O730" t="inlineStr">
@@ -51495,7 +51495,7 @@
         </is>
       </c>
       <c r="P730" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="R730" t="n">
         <v>57</v>
@@ -51511,11 +51511,11 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>1961717</v>
+        <v>1961718</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Nurul Alom Barbhuiya</t>
+          <t>Nasir Uddin Barbhuiya</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>Nurul Alom Barbhuiya</t>
+          <t>Nasir Uddin Barbhuiya</t>
         </is>
       </c>
       <c r="L731" t="inlineStr">
@@ -51558,7 +51558,7 @@
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O731" t="inlineStr">
@@ -51567,7 +51567,7 @@
         </is>
       </c>
       <c r="P731" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R731" t="n">
         <v>57</v>
@@ -51630,7 +51630,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
@@ -51702,7 +51702,7 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O733" t="inlineStr">
@@ -51846,7 +51846,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
@@ -51918,7 +51918,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O736" t="inlineStr">
@@ -51990,7 +51990,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
@@ -52265,7 +52265,7 @@
       </c>
       <c r="N741" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O741" t="inlineStr">
@@ -52337,7 +52337,7 @@
       </c>
       <c r="N742" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O742" t="inlineStr">
@@ -52409,7 +52409,7 @@
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O743" t="inlineStr">
@@ -52481,7 +52481,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O744" t="inlineStr">
@@ -52553,7 +52553,7 @@
       </c>
       <c r="N745" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O745" t="inlineStr">
@@ -52684,7 +52684,7 @@
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O747" t="inlineStr">
@@ -52756,7 +52756,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O748" t="inlineStr">
@@ -52828,7 +52828,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O749" t="inlineStr">
@@ -52972,7 +52972,7 @@
       </c>
       <c r="N751" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O751" t="inlineStr">
@@ -53044,7 +53044,7 @@
       </c>
       <c r="N752" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O752" t="inlineStr">
@@ -53116,7 +53116,7 @@
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O753" t="inlineStr">
@@ -53188,7 +53188,7 @@
       </c>
       <c r="N754" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O754" t="inlineStr">
@@ -53319,7 +53319,7 @@
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O756" t="inlineStr">
@@ -53391,7 +53391,7 @@
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O757" t="inlineStr">
@@ -53463,7 +53463,7 @@
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O758" t="inlineStr">
@@ -53535,7 +53535,7 @@
       </c>
       <c r="N759" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O759" t="inlineStr">
@@ -53679,7 +53679,7 @@
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O761" t="inlineStr">
@@ -53751,7 +53751,7 @@
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O762" t="inlineStr">
@@ -53823,7 +53823,7 @@
       </c>
       <c r="N763" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O763" t="inlineStr">
@@ -53895,7 +53895,7 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O764" t="inlineStr">
@@ -54386,7 +54386,7 @@
       </c>
       <c r="N771" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O771" t="inlineStr">
@@ -54517,7 +54517,7 @@
       </c>
       <c r="N773" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O773" t="inlineStr">
@@ -54589,7 +54589,7 @@
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O774" t="inlineStr">
@@ -54733,7 +54733,7 @@
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O776" t="inlineStr">
@@ -54805,7 +54805,7 @@
       </c>
       <c r="N777" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O777" t="inlineStr">
@@ -54877,7 +54877,7 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O778" t="inlineStr">
@@ -54949,7 +54949,7 @@
       </c>
       <c r="N779" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O779" t="inlineStr">
@@ -55021,7 +55021,7 @@
       </c>
       <c r="N780" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O780" t="inlineStr">
@@ -55093,7 +55093,7 @@
       </c>
       <c r="N781" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O781" t="inlineStr">
@@ -55237,7 +55237,7 @@
       </c>
       <c r="N783" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O783" t="inlineStr">
@@ -55309,7 +55309,7 @@
       </c>
       <c r="N784" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O784" t="inlineStr">
@@ -55381,7 +55381,7 @@
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O785" t="inlineStr">
@@ -55453,7 +55453,7 @@
       </c>
       <c r="N786" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O786" t="inlineStr">
@@ -55525,7 +55525,7 @@
       </c>
       <c r="N787" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O787" t="inlineStr">
@@ -55656,7 +55656,7 @@
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O789" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="N790" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O790" t="inlineStr">
@@ -55800,7 +55800,7 @@
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O791" t="inlineStr">
@@ -55872,7 +55872,7 @@
       </c>
       <c r="N792" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O792" t="inlineStr">
@@ -55944,7 +55944,7 @@
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O793" t="inlineStr">
@@ -56016,7 +56016,7 @@
       </c>
       <c r="N794" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O794" t="inlineStr">
@@ -56088,7 +56088,7 @@
       </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O795" t="inlineStr">
@@ -56160,7 +56160,7 @@
       </c>
       <c r="N796" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O796" t="inlineStr">
@@ -56232,7 +56232,7 @@
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O797" t="inlineStr">
@@ -56304,7 +56304,7 @@
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O798" t="inlineStr">
@@ -56376,7 +56376,7 @@
       </c>
       <c r="N799" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O799" t="inlineStr">
@@ -56448,7 +56448,7 @@
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O800" t="inlineStr">
@@ -56520,7 +56520,7 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O801" t="inlineStr">
@@ -56651,7 +56651,7 @@
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O803" t="inlineStr">
@@ -56723,7 +56723,7 @@
       </c>
       <c r="N804" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O804" t="inlineStr">
@@ -56795,7 +56795,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O805" t="inlineStr">
@@ -56867,7 +56867,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O806" t="inlineStr">
@@ -56939,7 +56939,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O807" t="inlineStr">
@@ -57011,7 +57011,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O808" t="inlineStr">
@@ -57083,7 +57083,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O809" t="inlineStr">
@@ -57155,7 +57155,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O810" t="inlineStr">
@@ -57227,7 +57227,7 @@
       </c>
       <c r="N811" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O811" t="inlineStr">
@@ -57299,7 +57299,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O812" t="inlineStr">
@@ -57371,7 +57371,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O813" t="inlineStr">
@@ -57443,7 +57443,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O814" t="inlineStr">
@@ -57515,7 +57515,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O815" t="inlineStr">
@@ -57587,7 +57587,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O816" t="inlineStr">
@@ -57659,7 +57659,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O817" t="inlineStr">
@@ -57790,7 +57790,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O819" t="inlineStr">
@@ -57934,7 +57934,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O821" t="inlineStr">
@@ -58006,7 +58006,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O822" t="inlineStr">
@@ -58078,7 +58078,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O823" t="inlineStr">
@@ -58150,7 +58150,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O824" t="inlineStr">
@@ -58222,7 +58222,7 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O825" t="inlineStr">
@@ -58294,7 +58294,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O826" t="inlineStr">
@@ -58366,7 +58366,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O827" t="inlineStr">
@@ -58438,7 +58438,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O828" t="inlineStr">
@@ -58510,7 +58510,7 @@
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O829" t="inlineStr">
@@ -58582,7 +58582,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O830" t="inlineStr">
@@ -58654,7 +58654,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O831" t="inlineStr">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O833" t="inlineStr">
@@ -58857,7 +58857,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O834" t="inlineStr">
@@ -58929,7 +58929,7 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O835" t="inlineStr">
@@ -59001,7 +59001,7 @@
       </c>
       <c r="N836" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O836" t="inlineStr">
@@ -59073,7 +59073,7 @@
       </c>
       <c r="N837" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O837" t="inlineStr">
@@ -59145,7 +59145,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O838" t="inlineStr">
@@ -59217,7 +59217,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O839" t="inlineStr">
